--- a/nr-update-system-nss/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-update-system-nss/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
+++ b/nr-update-system-nss/ig/ValueSet-fr-core-vs-organization-identifier-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Identifiant externe</t>
+  </si>
+  <si>
+    <t>RPPSRG</t>
+  </si>
+  <si>
+    <t>Identifiant RPPS Rang</t>
   </si>
   <si>
     <t/>
@@ -425,7 +431,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -501,15 +507,23 @@
         <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
